--- a/rate_table.xlsx
+++ b/rate_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{748EA30A-EC7A-4060-97B7-1E3DBE64E55B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB6F5B6B-C4FE-43EC-A9A9-E0FFDE0E0015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1300" yWindow="20" windowWidth="16280" windowHeight="9460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="34">
   <si>
     <t>起运港</t>
   </si>
@@ -84,47 +84,59 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>港务港建</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>订舱费</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>THC</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>按箱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>250/350</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>600/1200</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>80/160</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>每箱收</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RMB</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>船公司</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>备注</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>MSK</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>港务港建</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>订舱费</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>THC</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>按箱</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>250/350</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>600/1200</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>80/160</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>每箱收</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>RMB</t>
+    <t>船期</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>船名航次</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -504,113 +516,126 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="16" customWidth="1"/>
-    <col min="3" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="17.26953125" customWidth="1"/>
+    <col min="1" max="4" width="16" customWidth="1"/>
+    <col min="5" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="17.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2">
+      <c r="E2" s="2">
         <v>1200</v>
       </c>
-      <c r="D2" s="2">
+      <c r="F2" s="2">
         <v>2200</v>
       </c>
-      <c r="E2" s="2">
+      <c r="G2" s="2">
         <v>2300</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="4"/>
+    </row>
+    <row r="3" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2">
+      <c r="E3" s="2">
         <v>1300</v>
       </c>
-      <c r="D3" s="2">
+      <c r="F3" s="2">
         <v>2300</v>
       </c>
-      <c r="E3" s="2">
+      <c r="G3" s="2">
         <v>2400</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="4"/>
+    </row>
+    <row r="4" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="2">
+      <c r="E4" s="2">
         <v>1500</v>
       </c>
-      <c r="D4" s="2">
+      <c r="F4" s="2">
         <v>2800</v>
       </c>
-      <c r="E4" s="2">
+      <c r="G4" s="2">
         <v>2900</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="4"/>
+    </row>
+    <row r="5" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="2">
+      <c r="E5" s="2">
         <v>1350</v>
       </c>
-      <c r="D5" s="2">
+      <c r="F5" s="2">
         <v>2450</v>
       </c>
-      <c r="E5" s="2">
+      <c r="G5" s="2">
         <v>2550</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>21</v>
-      </c>
+      <c r="H5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -620,14 +645,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr defaultColWidth="15.6328125" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -646,39 +665,39 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
         <v>23</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -689,13 +708,13 @@
         <v>100</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -706,29 +725,40 @@
         <v>100</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>30</v>
-      </c>
       <c r="E6" t="s">
-        <v>29</v>
-      </c>
-    </row>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
